--- a/ycyk_analyzer/spec/spec_merged_20260914.xlsx
+++ b/ycyk_analyzer/spec/spec_merged_20260914.xlsx
@@ -7458,11 +7458,6 @@
         </is>
       </c>
     </row>
-    <row r="110"/>
-    <row r="111"/>
-    <row r="112"/>
-    <row r="113"/>
-    <row r="114"/>
     <row r="115">
       <c r="K115" s="5" t="inlineStr">
         <is>
@@ -19053,12 +19048,6 @@
         </is>
       </c>
     </row>
-    <row r="122"/>
-    <row r="123"/>
-    <row r="124"/>
-    <row r="125"/>
-    <row r="126"/>
-    <row r="127"/>
     <row r="128">
       <c r="K128" s="5" t="inlineStr">
         <is>
@@ -27959,15 +27948,6 @@
         </is>
       </c>
     </row>
-    <row r="148"/>
-    <row r="149"/>
-    <row r="150"/>
-    <row r="151"/>
-    <row r="152"/>
-    <row r="153"/>
-    <row r="154"/>
-    <row r="155"/>
-    <row r="156"/>
     <row r="157">
       <c r="K157" s="5" t="inlineStr">
         <is>
@@ -28828,7 +28808,7 @@
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>总体:按历史基线,级:告警</t>
+          <t>无需判据</t>
         </is>
       </c>
     </row>
@@ -28850,7 +28830,7 @@
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>总体:按历史基线,级:告警</t>
+          <t>无需判据</t>
         </is>
       </c>
     </row>
@@ -28872,7 +28852,7 @@
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>总体:按历史基线,级:告警</t>
+          <t>无需判据</t>
         </is>
       </c>
     </row>
@@ -28894,7 +28874,7 @@
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>总体:按历史基线,级:告警</t>
+          <t>无需判据</t>
         </is>
       </c>
     </row>
@@ -28916,7 +28896,7 @@
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>总体:按历史基线,级:告警</t>
+          <t>无需判据</t>
         </is>
       </c>
     </row>
@@ -28938,7 +28918,7 @@
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>总体:按历史基线,级:告警</t>
+          <t>无需判据</t>
         </is>
       </c>
     </row>
@@ -28960,7 +28940,7 @@
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>总体:按历史基线,级:告警</t>
+          <t>无需判据</t>
         </is>
       </c>
     </row>
@@ -28982,7 +28962,7 @@
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>总体:按历史基线,级:告警</t>
+          <t>无需判据</t>
         </is>
       </c>
     </row>
@@ -29004,7 +28984,7 @@
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>总体:按历史基线,级:告警</t>
+          <t>无需判据</t>
         </is>
       </c>
     </row>
@@ -29026,7 +29006,7 @@
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>总体:按历史基线,级:告警</t>
+          <t>无需判据</t>
         </is>
       </c>
     </row>
@@ -29048,7 +29028,7 @@
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>总体:按历史基线,级:告警</t>
+          <t>无需判据</t>
         </is>
       </c>
     </row>
@@ -29070,7 +29050,7 @@
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>总体:按历史基线,级:告警</t>
+          <t>无需判据</t>
         </is>
       </c>
     </row>
@@ -29092,7 +29072,7 @@
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>总体:按历史基线,级:告警</t>
+          <t>无需判据</t>
         </is>
       </c>
     </row>
@@ -29114,7 +29094,7 @@
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>总体:按历史基线,级:告警</t>
+          <t>无需判据</t>
         </is>
       </c>
     </row>
@@ -29136,7 +29116,7 @@
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>总体:按历史基线,级:告警</t>
+          <t>无需判据</t>
         </is>
       </c>
     </row>
@@ -29158,7 +29138,7 @@
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>总体:按历史基线,级:告警</t>
+          <t>无需判据</t>
         </is>
       </c>
     </row>
@@ -29180,7 +29160,7 @@
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>总体:按历史基线,级:告警</t>
+          <t>无需判据</t>
         </is>
       </c>
     </row>
@@ -29202,7 +29182,7 @@
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>总体:按历史基线,级:告警</t>
+          <t>无需判据</t>
         </is>
       </c>
     </row>
@@ -29224,7 +29204,7 @@
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>总体:按历史基线,级:告警</t>
+          <t>无需判据</t>
         </is>
       </c>
     </row>
@@ -29246,7 +29226,7 @@
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>总体:按历史基线,级:告警</t>
+          <t>无需判据</t>
         </is>
       </c>
     </row>
@@ -29268,7 +29248,7 @@
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>总体:按历史基线,级:告警</t>
+          <t>无需判据</t>
         </is>
       </c>
     </row>
@@ -29290,7 +29270,7 @@
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>总体:按历史基线,级:告警</t>
+          <t>无需判据</t>
         </is>
       </c>
     </row>

--- a/ycyk_analyzer/spec/spec_merged_20260914.xlsx
+++ b/ycyk_analyzer/spec/spec_merged_20260914.xlsx
@@ -30561,7 +30561,7 @@
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>待定(0914实测192.0~205.0)</t>
+          <t>无需判据</t>
         </is>
       </c>
     </row>

--- a/ycyk_analyzer/spec/spec_merged_20260914.xlsx
+++ b/ycyk_analyzer/spec/spec_merged_20260914.xlsx
@@ -28220,7 +28220,7 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>正常值:1,级:异常</t>
+          <t>无需判据</t>
         </is>
       </c>
     </row>
@@ -28242,7 +28242,7 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>正常值:1,级:异常</t>
+          <t>无需判据</t>
         </is>
       </c>
     </row>
@@ -28264,7 +28264,7 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>正常值:1,级:异常</t>
+          <t>无需判据</t>
         </is>
       </c>
     </row>
@@ -28286,7 +28286,7 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>正常值:1,级:异常</t>
+          <t>无需判据</t>
         </is>
       </c>
     </row>
@@ -28308,7 +28308,7 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>正常值:1,级:异常</t>
+          <t>无需判据</t>
         </is>
       </c>
     </row>
@@ -29820,7 +29820,7 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>正常范围:1.36~1.43,级:异常</t>
+          <t>正常范围:1.0~1.8,级:异常</t>
         </is>
       </c>
     </row>
@@ -29842,7 +29842,7 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>正常范围:1.53~1.71,级:异常</t>
+          <t>正常范围:1.1~2.0,级:异常</t>
         </is>
       </c>
     </row>
@@ -29864,7 +29864,7 @@
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>正常范围:2.21~2.28,级:异常</t>
+          <t>正常范围:1.6~2.9,级:异常</t>
         </is>
       </c>
     </row>
@@ -29908,7 +29908,7 @@
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>正常范围:1.86~2.13,级:异常</t>
+          <t>正常范围:1.3~2.5,级:异常</t>
         </is>
       </c>
     </row>

--- a/ycyk_analyzer/spec/spec_merged_20260914.xlsx
+++ b/ycyk_analyzer/spec/spec_merged_20260914.xlsx
@@ -7460,6 +7460,11 @@
         </is>
       </c>
     </row>
+    <row r="110"/>
+    <row r="111"/>
+    <row r="112"/>
+    <row r="113"/>
+    <row r="114"/>
     <row r="115">
       <c r="K115" s="6" t="inlineStr">
         <is>
@@ -12291,6 +12296,19 @@
         </is>
       </c>
     </row>
+    <row r="92"/>
+    <row r="93"/>
+    <row r="94"/>
+    <row r="95"/>
+    <row r="96"/>
+    <row r="97"/>
+    <row r="98"/>
+    <row r="99"/>
+    <row r="100"/>
+    <row r="101"/>
+    <row r="102"/>
+    <row r="103"/>
+    <row r="104"/>
     <row r="105">
       <c r="K105" s="6" t="inlineStr">
         <is>
@@ -19050,6 +19068,12 @@
         </is>
       </c>
     </row>
+    <row r="122"/>
+    <row r="123"/>
+    <row r="124"/>
+    <row r="125"/>
+    <row r="126"/>
+    <row r="127"/>
     <row r="128">
       <c r="K128" s="6" t="inlineStr">
         <is>
@@ -27950,6 +27974,15 @@
         </is>
       </c>
     </row>
+    <row r="148"/>
+    <row r="149"/>
+    <row r="150"/>
+    <row r="151"/>
+    <row r="152"/>
+    <row r="153"/>
+    <row r="154"/>
+    <row r="155"/>
+    <row r="156"/>
     <row r="157">
       <c r="K157" s="6" t="inlineStr">
         <is>
@@ -28065,9 +28098,9 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>0b00：默认AB同时工作
-0b01：关闭B总线，仅A总线工作
-0b10：关闭A总线，仅B总线工作</t>
+          <t>00：默认AB同时工作
+01：关闭B总线，仅A总线工作
+10：关闭A总线，仅B总线工作</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
@@ -28106,8 +28139,8 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>0b00：A总线
-0b11：B总线</t>
+          <t>00：A总线
+11：B总线</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
@@ -28169,11 +28202,11 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>0000b：待机模式
-0001b：常规业务模式
-0010b：高性能业务模式
-0011b：自定义业务模式
-0100b：维护模式</t>
+          <t>0000：待机模式
+0001：常规业务模式
+0010：高性能业务模式
+0011：自定义业务模式
+0100：维护模式</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
@@ -28713,7 +28746,7 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>1b：申请断电；0b：无断电申请</t>
+          <t>1：申请断电；0：无断电申请</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
@@ -31773,7 +31806,7 @@
       </c>
       <c r="C105" s="6" t="inlineStr">
         <is>
-          <t>0b:正常；1b：异常</t>
+          <t>0:正常；1：异常</t>
         </is>
       </c>
       <c r="D105" s="6" t="inlineStr">
@@ -31795,7 +31828,7 @@
       </c>
       <c r="C106" s="6" t="inlineStr">
         <is>
-          <t>0b:正常；1b：异常</t>
+          <t>0:正常；1：异常</t>
         </is>
       </c>
       <c r="D106" s="6" t="inlineStr">
@@ -31817,7 +31850,7 @@
       </c>
       <c r="C107" s="6" t="inlineStr">
         <is>
-          <t>0b:正常；1b：异常</t>
+          <t>0:正常；1：异常</t>
         </is>
       </c>
       <c r="D107" s="6" t="inlineStr">

--- a/ycyk_analyzer/spec/spec_merged_20260914.xlsx
+++ b/ycyk_analyzer/spec/spec_merged_20260914.xlsx
@@ -7460,11 +7460,6 @@
         </is>
       </c>
     </row>
-    <row r="110"/>
-    <row r="111"/>
-    <row r="112"/>
-    <row r="113"/>
-    <row r="114"/>
     <row r="115">
       <c r="K115" s="6" t="inlineStr">
         <is>
@@ -12296,19 +12291,6 @@
         </is>
       </c>
     </row>
-    <row r="92"/>
-    <row r="93"/>
-    <row r="94"/>
-    <row r="95"/>
-    <row r="96"/>
-    <row r="97"/>
-    <row r="98"/>
-    <row r="99"/>
-    <row r="100"/>
-    <row r="101"/>
-    <row r="102"/>
-    <row r="103"/>
-    <row r="104"/>
     <row r="105">
       <c r="K105" s="6" t="inlineStr">
         <is>
@@ -19068,12 +19050,6 @@
         </is>
       </c>
     </row>
-    <row r="122"/>
-    <row r="123"/>
-    <row r="124"/>
-    <row r="125"/>
-    <row r="126"/>
-    <row r="127"/>
     <row r="128">
       <c r="K128" s="6" t="inlineStr">
         <is>
@@ -27974,15 +27950,6 @@
         </is>
       </c>
     </row>
-    <row r="148"/>
-    <row r="149"/>
-    <row r="150"/>
-    <row r="151"/>
-    <row r="152"/>
-    <row r="153"/>
-    <row r="154"/>
-    <row r="155"/>
-    <row r="156"/>
     <row r="157">
       <c r="K157" s="6" t="inlineStr">
         <is>
@@ -28185,7 +28152,7 @@
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>文本:异常/失败/错误,级:异常</t>
+          <t>无需判据</t>
         </is>
       </c>
     </row>
@@ -28365,7 +28332,7 @@
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>正常值:1,级:异常</t>
+          <t>无需判据</t>
         </is>
       </c>
     </row>
@@ -28387,7 +28354,7 @@
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>正常值:1,级:异常</t>
+          <t>无需判据</t>
         </is>
       </c>
     </row>
@@ -29921,7 +29888,7 @@
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>正常范围:0.83~0.83,级:异常</t>
+          <t>正常范围:0.82~0.84,级:异常</t>
         </is>
       </c>
     </row>

--- a/ycyk_analyzer/spec/spec_merged_20260914.xlsx
+++ b/ycyk_analyzer/spec/spec_merged_20260914.xlsx
@@ -28178,7 +28178,7 @@
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>正常值:常规业务模式,级:异常</t>
+          <t>无需判据</t>
         </is>
       </c>
     </row>
@@ -28200,7 +28200,7 @@
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>正常值:1,级:异常</t>
+          <t>无需判据</t>
         </is>
       </c>
     </row>
@@ -28467,7 +28467,7 @@
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>文本:异常|失败|故障|过高|过低,级:异常</t>
+          <t>无需判据</t>
         </is>
       </c>
     </row>
